--- a/DevStackAutomationFramework/src/test/resources/excelData/LoginTest.xlsx
+++ b/DevStackAutomationFramework/src/test/resources/excelData/LoginTest.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\WW\IdeaProjects\DevStackAutomationFramework\DevStackAutomationFramework\src\test\resources\excelData\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3E4DAF78-A45E-4059-A1B8-93B62A9E602F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A7A3E9C9-5C47-4C20-9E01-B58052C89D3D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="0" windowWidth="20490" windowHeight="10920" xr2:uid="{1BC3C561-4519-DC4B-97F5-0E0D12BD283E}"/>
   </bookViews>
@@ -34,7 +34,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="40" uniqueCount="22">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="40" uniqueCount="23">
   <si>
     <t>admin</t>
   </si>
@@ -100,6 +100,9 @@
   </si>
   <si>
     <t>Empty Password</t>
+  </si>
+  <si>
+    <t>fail</t>
   </si>
 </sst>
 </file>
@@ -581,7 +584,7 @@
         <v>1</v>
       </c>
       <c r="E4" s="2" t="s">
-        <v>8</v>
+        <v>22</v>
       </c>
       <c r="F4" s="2" t="s">
         <v>12</v>
@@ -601,7 +604,7 @@
         <v>9</v>
       </c>
       <c r="E5" s="2" t="s">
-        <v>8</v>
+        <v>22</v>
       </c>
       <c r="F5" s="2" t="s">
         <v>13</v>
@@ -619,7 +622,7 @@
         <v>1</v>
       </c>
       <c r="E6" s="2" t="s">
-        <v>8</v>
+        <v>22</v>
       </c>
       <c r="F6" s="2" t="s">
         <v>12</v>
@@ -637,7 +640,7 @@
       </c>
       <c r="D7" s="2"/>
       <c r="E7" s="2" t="s">
-        <v>8</v>
+        <v>22</v>
       </c>
       <c r="F7" s="2" t="s">
         <v>12</v>

--- a/DevStackAutomationFramework/src/test/resources/excelData/LoginTest.xlsx
+++ b/DevStackAutomationFramework/src/test/resources/excelData/LoginTest.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\WW\IdeaProjects\DevStackAutomationFramework\DevStackAutomationFramework\src\test\resources\excelData\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A7A3E9C9-5C47-4C20-9E01-B58052C89D3D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E1F2FEB2-C457-454B-8631-3E91AF51D47B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="0" windowWidth="20490" windowHeight="10920" xr2:uid="{1BC3C561-4519-DC4B-97F5-0E0D12BD283E}"/>
   </bookViews>

--- a/DevStackAutomationFramework/src/test/resources/excelData/LoginTest.xlsx
+++ b/DevStackAutomationFramework/src/test/resources/excelData/LoginTest.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\WW\IdeaProjects\DevStackAutomationFramework\DevStackAutomationFramework\src\test\resources\excelData\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E1F2FEB2-C457-454B-8631-3E91AF51D47B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CC260EE8-6AD2-46F4-ABA9-03272BE940C7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="0" windowWidth="20490" windowHeight="10920" xr2:uid="{1BC3C561-4519-DC4B-97F5-0E0D12BD283E}"/>
   </bookViews>
@@ -34,7 +34,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="40" uniqueCount="23">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="50" uniqueCount="25">
   <si>
     <t>admin</t>
   </si>
@@ -51,84 +51,76 @@
     <t>super@admin.com</t>
   </si>
   <si>
+    <t>student1@library.com</t>
+  </si>
+  <si>
+    <t>expectedResult</t>
+  </si>
+  <si>
+    <t>success</t>
+  </si>
+  <si>
+    <t>wrong123</t>
+  </si>
+  <si>
+    <t>validationType</t>
+  </si>
+  <si>
+    <t>none</t>
+  </si>
+  <si>
+    <t>browser</t>
+  </si>
+  <si>
+    <t>system</t>
+  </si>
+  <si>
+    <t>testCaseName</t>
+  </si>
+  <si>
+    <t>Valid Admin Login</t>
+  </si>
+  <si>
+    <t>Valid Student Login</t>
+  </si>
+  <si>
+    <t>Invalid Email Format</t>
+  </si>
+  <si>
+    <t>wrong</t>
+  </si>
+  <si>
+    <t>Invalid Password</t>
+  </si>
+  <si>
+    <t>Empty Email</t>
+  </si>
+  <si>
+    <t>Empty Password</t>
+  </si>
+  <si>
+    <t>fail</t>
+  </si>
+  <si>
+    <t>Empty Fields</t>
+  </si>
+  <si>
+    <t>Valid Email Login</t>
+  </si>
+  <si>
     <t>student</t>
-  </si>
-  <si>
-    <t>student1@library.com</t>
-  </si>
-  <si>
-    <t>expectedResult</t>
-  </si>
-  <si>
-    <t>success</t>
-  </si>
-  <si>
-    <t>wrong123</t>
-  </si>
-  <si>
-    <t>validationType</t>
-  </si>
-  <si>
-    <t>none</t>
-  </si>
-  <si>
-    <t>browser</t>
-  </si>
-  <si>
-    <t>system</t>
-  </si>
-  <si>
-    <t>testCaseName</t>
-  </si>
-  <si>
-    <t>Valid Admin Login</t>
-  </si>
-  <si>
-    <t>Valid Student Login</t>
-  </si>
-  <si>
-    <t>Invalid Email Format</t>
-  </si>
-  <si>
-    <t>wrong</t>
-  </si>
-  <si>
-    <t>Invalid Password</t>
-  </si>
-  <si>
-    <t>Empty Email</t>
-  </si>
-  <si>
-    <t>Empty Password</t>
-  </si>
-  <si>
-    <t>fail</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="3">
+  <fonts count="1">
     <font>
       <sz val="12"/>
       <color theme="1"/>
       <name val="Aptos Narrow"/>
       <family val="2"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <u/>
-      <sz val="12"/>
-      <color theme="10"/>
-      <name val="Aptos Narrow"/>
-      <family val="2"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="12"/>
-      <color theme="1"/>
-      <name val="Aptos Narrow"/>
       <scheme val="minor"/>
     </font>
   </fonts>
@@ -149,24 +141,16 @@
       <diagonal/>
     </border>
   </borders>
-  <cellStyleXfs count="2">
+  <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="4">
+  <cellXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
   </cellXfs>
-  <cellStyles count="2">
-    <cellStyle name="Hyperlink" xfId="1" builtinId="8"/>
+  <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="0"/>
@@ -499,7 +483,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{FF8FA32C-E2EF-4D4E-A323-FA8DBCB49818}">
-  <dimension ref="A1:F7"/>
+  <dimension ref="A1:F9"/>
   <sheetFormatPr defaultColWidth="11.5546875" defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="16.77734375" bestFit="1" customWidth="1"/>
@@ -512,148 +496,174 @@
   <sheetData>
     <row r="1" spans="1:6">
       <c r="A1" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="B1" t="s">
+        <v>2</v>
+      </c>
+      <c r="C1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D1" t="s">
+        <v>1</v>
+      </c>
+      <c r="E1" t="s">
+        <v>6</v>
+      </c>
+      <c r="F1" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="2" spans="1:6">
+      <c r="A2" t="s">
         <v>14</v>
       </c>
-      <c r="B1" s="1" t="s">
-        <v>2</v>
-      </c>
-      <c r="C1" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D1" s="1" t="s">
+      <c r="B2" t="s">
+        <v>0</v>
+      </c>
+      <c r="C2" t="s">
+        <v>4</v>
+      </c>
+      <c r="D2" t="s">
         <v>1</v>
       </c>
-      <c r="E1" s="1" t="s">
+      <c r="E2" t="s">
         <v>7</v>
       </c>
-      <c r="F1" s="1" t="s">
+      <c r="F2" t="s">
         <v>10</v>
       </c>
     </row>
-    <row r="2" spans="1:6">
-      <c r="A2" s="2" t="s">
+    <row r="3" spans="1:6">
+      <c r="A3" t="s">
         <v>15</v>
       </c>
-      <c r="B2" s="2" t="s">
+      <c r="B3" t="s">
+        <v>24</v>
+      </c>
+      <c r="C3" t="s">
+        <v>5</v>
+      </c>
+      <c r="D3" t="s">
+        <v>1</v>
+      </c>
+      <c r="E3" t="s">
+        <v>7</v>
+      </c>
+      <c r="F3" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="4" spans="1:6">
+      <c r="A4" t="s">
+        <v>16</v>
+      </c>
+      <c r="B4" t="s">
         <v>0</v>
       </c>
-      <c r="C2" s="3" t="s">
+      <c r="C4" t="s">
+        <v>17</v>
+      </c>
+      <c r="D4" t="s">
+        <v>1</v>
+      </c>
+      <c r="E4" t="s">
+        <v>21</v>
+      </c>
+      <c r="F4" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="5" spans="1:6">
+      <c r="A5" t="s">
+        <v>18</v>
+      </c>
+      <c r="B5" t="s">
+        <v>0</v>
+      </c>
+      <c r="C5" t="s">
         <v>4</v>
       </c>
-      <c r="D2" s="2" t="s">
+      <c r="D5" t="s">
+        <v>8</v>
+      </c>
+      <c r="E5" t="s">
+        <v>21</v>
+      </c>
+      <c r="F5" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="6" spans="1:6">
+      <c r="A6" t="s">
+        <v>19</v>
+      </c>
+      <c r="B6" t="s">
+        <v>0</v>
+      </c>
+      <c r="D6" t="s">
         <v>1</v>
       </c>
-      <c r="E2" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="F2" s="2" t="s">
+      <c r="E6" t="s">
+        <v>21</v>
+      </c>
+      <c r="F6" t="s">
         <v>11</v>
       </c>
     </row>
-    <row r="3" spans="1:6">
-      <c r="A3" s="2" t="s">
-        <v>16</v>
-      </c>
-      <c r="B3" s="2" t="s">
-        <v>5</v>
-      </c>
-      <c r="C3" s="3" t="s">
-        <v>6</v>
-      </c>
-      <c r="D3" s="2" t="s">
+    <row r="7" spans="1:6">
+      <c r="A7" t="s">
+        <v>20</v>
+      </c>
+      <c r="B7" t="s">
+        <v>0</v>
+      </c>
+      <c r="C7" t="s">
+        <v>4</v>
+      </c>
+      <c r="E7" t="s">
+        <v>21</v>
+      </c>
+      <c r="F7" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="8" spans="1:6">
+      <c r="A8" t="s">
+        <v>22</v>
+      </c>
+      <c r="B8" t="s">
+        <v>0</v>
+      </c>
+      <c r="E8" t="s">
+        <v>21</v>
+      </c>
+      <c r="F8" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="9" spans="1:6">
+      <c r="A9" t="s">
+        <v>23</v>
+      </c>
+      <c r="B9" t="s">
+        <v>0</v>
+      </c>
+      <c r="C9" t="s">
+        <v>4</v>
+      </c>
+      <c r="D9" t="s">
         <v>1</v>
       </c>
-      <c r="E3" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="F3" s="2" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="4" spans="1:6">
-      <c r="A4" s="2" t="s">
-        <v>17</v>
-      </c>
-      <c r="B4" s="2" t="s">
-        <v>0</v>
-      </c>
-      <c r="C4" s="2" t="s">
-        <v>18</v>
-      </c>
-      <c r="D4" s="2" t="s">
-        <v>1</v>
-      </c>
-      <c r="E4" s="2" t="s">
-        <v>22</v>
-      </c>
-      <c r="F4" s="2" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="5" spans="1:6">
-      <c r="A5" s="2" t="s">
-        <v>19</v>
-      </c>
-      <c r="B5" s="2" t="s">
-        <v>0</v>
-      </c>
-      <c r="C5" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="D5" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="E5" s="2" t="s">
-        <v>22</v>
-      </c>
-      <c r="F5" s="2" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="6" spans="1:6">
-      <c r="A6" s="2" t="s">
-        <v>20</v>
-      </c>
-      <c r="B6" s="2" t="s">
-        <v>0</v>
-      </c>
-      <c r="C6" s="2"/>
-      <c r="D6" s="2" t="s">
-        <v>1</v>
-      </c>
-      <c r="E6" s="2" t="s">
-        <v>22</v>
-      </c>
-      <c r="F6" s="2" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="7" spans="1:6">
-      <c r="A7" s="2" t="s">
-        <v>21</v>
-      </c>
-      <c r="B7" s="2" t="s">
-        <v>0</v>
-      </c>
-      <c r="C7" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="D7" s="2"/>
-      <c r="E7" s="2" t="s">
-        <v>22</v>
-      </c>
-      <c r="F7" s="2" t="s">
-        <v>12</v>
+      <c r="E9" t="s">
+        <v>7</v>
+      </c>
+      <c r="F9" t="s">
+        <v>10</v>
       </c>
     </row>
   </sheetData>
-  <hyperlinks>
-    <hyperlink ref="C2" r:id="rId1" display="mailto:super@admin.com" xr:uid="{CF1B7189-EBC2-44C9-940F-FC3510A9CEF5}"/>
-    <hyperlink ref="C3" r:id="rId2" display="mailto:student1@library.com" xr:uid="{05EA8E5A-95EC-43A6-A6E6-84F0B32C9AFC}"/>
-    <hyperlink ref="C5" r:id="rId3" display="mailto:super@admin.com" xr:uid="{EF5527C4-C296-4F16-83E6-B953CC432321}"/>
-    <hyperlink ref="C7" r:id="rId4" display="mailto:super@admin.com" xr:uid="{EC6B44B9-F94A-425B-AB39-CF560DF6FB4B}"/>
-  </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup orientation="portrait" r:id="rId5"/>
+  <pageSetup orientation="portrait" r:id="rId1"/>
 </worksheet>
 </file>